--- a/data/trans_orig/P6707-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6707-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>55639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24338</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71203</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53785</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81147</t>
+          <t>81307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115631</t>
+          <t>117356</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66465</t>
+          <t>67388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100720</t>
+          <t>99315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>31615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56663</t>
+          <t>57595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106299</t>
+          <t>107814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148409</t>
+          <t>149154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110260</t>
+          <t>108618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145509</t>
+          <t>143964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58349</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85483</t>
+          <t>86187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>176780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222329</t>
+          <t>220966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>61206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53238</t>
+          <t>54848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70005</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107062</t>
+          <t>106116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21082</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45052</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48540</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75835</t>
+          <t>76478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54259</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85008</t>
+          <t>84962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121309</t>
+          <t>121530</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84419</t>
+          <t>84644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39956</t>
+          <t>41512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>80269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118667</t>
+          <t>116106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120514</t>
+          <t>119381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57755</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34416</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47043</t>
+          <t>47334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74080</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>92696</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66309</t>
+          <t>66320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56349</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86780</t>
+          <t>87635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>97206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131267</t>
+          <t>131310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48271</t>
+          <t>48231</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>70176</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153351</t>
+          <t>154840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>192370</t>
+          <t>195331</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69353</t>
+          <t>72466</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106578</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75866</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126224</t>
+          <t>128020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171047</t>
+          <t>172176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>32290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57781</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>47284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63024</t>
+          <t>63629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99262</t>
+          <t>99933</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78896</t>
+          <t>78893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>114818</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87268</t>
+          <t>86730</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>143520</t>
+          <t>145805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>189878</t>
+          <t>191285</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57895</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>69614</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>109148</t>
+          <t>106879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149334</t>
+          <t>149491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104438</t>
+          <t>105987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145042</t>
+          <t>144751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>59523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91953</t>
+          <t>90401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>172940</t>
+          <t>172805</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225337</t>
+          <t>223997</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35689</t>
+          <t>35469</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94144</t>
+          <t>94004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>56213</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55114</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>19552</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57598</t>
+          <t>57397</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87332</t>
+          <t>87537</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26013</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>50110</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44216</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>47486</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54578</t>
+          <t>54831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>61913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>93408</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>189560</t>
+          <t>190643</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>245674</t>
+          <t>247061</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155532</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>206676</t>
+          <t>209338</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>356745</t>
+          <t>361762</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>434026</t>
+          <t>433926</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>97379</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>140796</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>109118</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>179181</t>
+          <t>179035</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>239003</t>
+          <t>233330</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>284444</t>
+          <t>285721</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>348286</t>
+          <t>349559</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>173629</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>225231</t>
+          <t>227503</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>473710</t>
+          <t>477862</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>558148</t>
+          <t>558185</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>268120</t>
+          <t>268904</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>331276</t>
+          <t>332621</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>156992</t>
+          <t>158630</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>209602</t>
+          <t>207835</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>439405</t>
+          <t>433837</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>523109</t>
+          <t>519728</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>426379</t>
+          <t>425394</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>498400</t>
+          <t>500208</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>259338</t>
+          <t>256260</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>314762</t>
+          <t>314695</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>701916</t>
+          <t>699983</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>799461</t>
+          <t>794516</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>45717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49780</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80571</t>
+          <t>78963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44557</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>48262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78136</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64009</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95053</t>
+          <t>95881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>111276</t>
+          <t>111501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149971</t>
+          <t>151562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71995</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>39287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61678</t>
+          <t>63868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90670</t>
+          <t>90709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127465</t>
+          <t>127102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95660</t>
+          <t>95184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>63781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108866</t>
+          <t>109832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149243</t>
+          <t>150234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>28014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>33878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55777</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99399</t>
+          <t>100997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32705</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58951</t>
+          <t>61027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>38754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59444</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91534</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57961</t>
+          <t>57093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87924</t>
+          <t>88867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59706</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100741</t>
+          <t>100543</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139364</t>
+          <t>138201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50997</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73006</t>
+          <t>73448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108481</t>
+          <t>107805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29652</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>55045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>87810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>33432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38388</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40985</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49887</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>78359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59333</t>
+          <t>60937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90388</t>
+          <t>89808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>44312</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>68933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61619</t>
+          <t>63184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92808</t>
+          <t>92130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63941</t>
+          <t>64783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69309</t>
+          <t>68917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101381</t>
+          <t>99242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94774</t>
+          <t>93184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131411</t>
+          <t>132108</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>73456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107847</t>
+          <t>106973</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176186</t>
+          <t>177936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224044</t>
+          <t>227381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98365</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>40158</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114420</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154916</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>101499</t>
+          <t>101132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>141491</t>
+          <t>139326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85793</t>
+          <t>85972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117880</t>
+          <t>118502</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>197545</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>250437</t>
+          <t>248425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84564</t>
+          <t>84777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120435</t>
+          <t>120928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62769</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95356</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158044</t>
+          <t>154976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>204756</t>
+          <t>203426</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58779</t>
+          <t>56702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90321</t>
+          <t>88563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>34544</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101147</t>
+          <t>99283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143264</t>
+          <t>140838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47957</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76520</t>
+          <t>76730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>32829</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57160</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88584</t>
+          <t>90352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124561</t>
+          <t>126336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46284</t>
+          <t>46839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>54460</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85704</t>
+          <t>84939</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>37741</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>62242</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>73131</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>90323</t>
+          <t>91084</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>125634</t>
+          <t>128091</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45256</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39419</t>
+          <t>39596</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>65370</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>41687</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>36037</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>71247</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>234333</t>
+          <t>229885</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292295</t>
+          <t>290552</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>188108</t>
+          <t>188186</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>241432</t>
+          <t>239799</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>436262</t>
+          <t>435068</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>514813</t>
+          <t>518183</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>194618</t>
+          <t>192846</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>251839</t>
+          <t>247089</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>124873</t>
+          <t>123787</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>169750</t>
+          <t>167417</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,47 +8630,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>365091</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>330483</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>402721</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>16,38%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>365091</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>331036</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>403215</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>348879</t>
+          <t>348486</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>420030</t>
+          <t>413632</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>245929</t>
+          <t>244912</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>301058</t>
+          <t>300137</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>610303</t>
+          <t>611331</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>699043</t>
+          <t>702333</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>256008</t>
+          <t>254153</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>320635</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>194357</t>
+          <t>193743</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>248986</t>
+          <t>248158</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>465351</t>
+          <t>467352</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>546868</t>
+          <t>546632</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>244228</t>
+          <t>243741</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>304800</t>
+          <t>303839</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>158129</t>
+          <t>159759</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>209460</t>
+          <t>209007</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>420355</t>
+          <t>421264</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>500248</t>
+          <t>500493</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,67 +9638,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>29,85%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>38503</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>28984</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>51419</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>15,51%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>37710</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>27595</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>49636</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17049</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>43651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64276</t>
+          <t>70233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>42503</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32663</t>
+          <t>37408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>58497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>19066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>253011</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>298356</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>257190</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316922</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,32 +10889,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119820</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>23573</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79074</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87857</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107443</t>
+          <t>45245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>32141</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43357</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39402</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70508</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84641</t>
+          <t>93161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>67809</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>54996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>41356</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55266</t>
+          <t>58625</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>13311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>32711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>116555</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>228321</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>228321</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>228321</t>
+          <t>251017</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>52218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,67 +12140,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>44684</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>73418</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>57716</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>89360</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>48,96%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>54081</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>42001</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>67471</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>28845</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>42106</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>347829</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>154491</t>
+          <t>99629</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>540757</t>
+          <t>143337</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>111774</t>
+          <t>129728</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>112282</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>147782</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>459603</t>
+          <t>250200</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>273693</t>
+          <t>222134</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>704029</t>
+          <t>277776</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>51689</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>74604</t>
+          <t>68266</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>46759</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>35640</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>66702</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>104976</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>87209</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>126807</t>
+          <t>127014</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>113143</t>
+          <t>121636</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>187968</t>
+          <t>145019</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>76905</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>64006</t>
+          <t>66747</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>190048</t>
+          <t>204084</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>105157</t>
+          <t>179922</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>262139</t>
+          <t>230247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>74054</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>65478</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>127581</t>
+          <t>100417</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67280</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>128578</t>
+          <t>139614</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>119410</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>177198</t>
+          <t>161869</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>85765</t>
+          <t>99089</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>145558</t>
+          <t>122553</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>46168</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>72251</t>
+          <t>78584</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>143739</t>
+          <t>162882</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74070</t>
+          <t>137163</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>196465</t>
+          <t>186888</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>347936</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>347936</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>347936</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1012262</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1012262</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1012262</t>
+          <t>861754</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
